--- a/db/logs_detection_ur3.xlsx
+++ b/db/logs_detection_ur3.xlsx
@@ -2,28 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="datalogs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="238"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -51,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -59,9 +65,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -424,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N102"/>
+  <dimension ref="A1:N113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -438,78 +447,78 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="29" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="12" max="13"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>id_detection</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>id_camera</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>ai_model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>hardware_setup</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>detection_start_time</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>detection_end_time</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>duration_s</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>average_fps</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>average_model_accuracy</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>average_inference_time_ms</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>tcp_x</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>tcp_y</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>tcp_z</t>
         </is>
@@ -5966,6 +5975,600 @@
         <v>0</v>
       </c>
       <c r="N102" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:06:29</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:06:42</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:06:44</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:06:44</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:06:44</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:06:44</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:06:46</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:07:13</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:07:17</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:07:27</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:07:32</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:07:45</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:07:48</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:07:53</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:07:55</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 17:08:04</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 22:17:23</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 22:17:32</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 22:17:33</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 22:17:35</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 22:17:37</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14 22:17:39</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/db/logs_detection_ur3.xlsx
+++ b/db/logs_detection_ur3.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N113"/>
+  <dimension ref="A1:N147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6572,6 +6572,1842 @@
         <v>0</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:41:49</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:41:49</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:41:49</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:41:49</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:41:52</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:41:52</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:41:52</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:41:52</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:41:53</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:41:53</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:04</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:06</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:09</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:11</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:14</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:17</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:18</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:21</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:22</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:25</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:27</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:30</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:31</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:37</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:39</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:39</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:08</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:11</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:13</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:16</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:18</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:20</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:22</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:25</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:27</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:29</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:31</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:36</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:38</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:38</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:38</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:38</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:39</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:39</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:58</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:58</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:54:58</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:55:02</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:55:04</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:55:04</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:18</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:18</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:18</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:18</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:19</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:19</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:20</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:20</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:22</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:22</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:23</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:23</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:24</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:25</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:26</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:27</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>requires checking</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>yolov8n-pose.pt</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>no cobot</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:28</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:58:28</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/db/logs_detection_ur3.xlsx
+++ b/db/logs_detection_ur3.xlsx
@@ -2,34 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="datalogs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="238"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -57,7 +51,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -65,12 +59,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -433,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N147"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -447,78 +438,78 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="29" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="13"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id_detection</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>id_camera</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ai_model</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>hardware_setup</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>detection_start_time</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>detection_end_time</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>duration_s</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>average_fps</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>average_model_accuracy</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>average_inference_time_ms</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tcp_x</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tcp_y</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>tcp_z</t>
         </is>
@@ -533,7 +524,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -543,39 +534,39 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:26</t>
+          <t>2026-06-16 11:19:49</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:26</t>
+          <t>2026-06-16 11:19:58</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.25</v>
+        <v>8.44</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>11.1</v>
+        <v>7.5</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>296.9571666819675</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>-253.8521207407773</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>159.9343225224462</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -597,39 +588,39 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:27</t>
+          <t>2026-06-16 11:19:58</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:33</t>
+          <t>2026-06-16 11:20:02</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>5.93</v>
+        <v>4.14</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>11.6</v>
+        <v>7.9</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.84</v>
+        <v>0.52</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>76.7</v>
+        <v>51.7</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>99.90756300659746</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>-353.828669227107</v>
+        <v>0</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>159.188441579429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -641,7 +632,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -651,39 +642,39 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:35</t>
+          <t>2026-06-16 11:20:03</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:35</t>
+          <t>2026-06-16 11:20:08</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>5.32</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>13.4</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.52</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>31.5</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>341.3397527273858</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>280.2562717224453</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>157.795804477444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -695,7 +686,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -705,39 +696,39 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:36</t>
+          <t>2026-06-16 11:20:08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:38</t>
+          <t>2026-06-16 11:20:09</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2.52</v>
+        <v>0.61</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>13.5</v>
+        <v>15.6</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.86</v>
+        <v>0.4</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>39.8</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>376.7113595730216</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>219.7623234980509</v>
+        <v>0</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>158.3087053211889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +740,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -759,39 +750,39 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:41</t>
+          <t>2026-06-16 11:20:09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:44</t>
+          <t>2026-06-16 11:20:09</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3.03</v>
+        <v>0.3</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>12.3</v>
+        <v>13.4</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.83</v>
+        <v>0.33</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>43.3</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-76.20152753324054</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-339.2996084881519</v>
+        <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>157.7763816271687</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -803,7 +794,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,39 +804,39 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:46</t>
+          <t>2026-06-16 11:20:09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:49</t>
+          <t>2026-06-16 11:20:09</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2.55</v>
+        <v>0.05</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>12.6</v>
+        <v>22</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.79</v>
+        <v>0.45</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>70.09999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>301.2788443372388</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>329.5740642279305</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>157.2795201292647</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -857,7 +848,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -867,39 +858,39 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:52</t>
+          <t>2026-06-16 11:20:09</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:52</t>
+          <t>2026-06-16 11:20:12</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.15</v>
+        <v>2.25</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11.7</v>
+        <v>14.1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.54</v>
+        <v>0.44</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>71.8</v>
+        <v>39.1</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>243.1125351940047</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-296.9921770766152</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>159.8146281694566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -921,39 +912,39 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:52</t>
+          <t>2026-06-16 11:20:12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:21:56</t>
+          <t>2026-06-16 11:20:15</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>4.42</v>
+        <v>3.47</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11.6</v>
+        <v>16.3</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>27</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-73.87175280977351</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-340.1063557425869</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>157.8014161737684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -965,7 +956,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -975,39 +966,39 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:00</t>
+          <t>2026-06-16 11:20:15</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:03</t>
+          <t>2026-06-16 11:20:16</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3.23</v>
+        <v>0.22</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>12.1</v>
+        <v>15.4</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.72</v>
+        <v>0.51</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>29.6</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>418.8146963824411</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>35.5154103342377</v>
+        <v>0</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>159.3782133447754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1029,39 +1020,39 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:05</t>
+          <t>2026-06-16 11:20:16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:06</t>
+          <t>2026-06-16 11:20:16</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>13.6</v>
+        <v>22.8</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.49</v>
+        <v>0.6</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>21.1</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-53.4076737511806</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-346.4084668884195</v>
+        <v>0</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>158.0123231021371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1073,7 +1064,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1083,39 +1074,39 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:06</t>
+          <t>2026-06-16 11:20:16</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:09</t>
+          <t>2026-06-16 11:20:16</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>3.21</v>
+        <v>0.04</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.79</v>
+        <v>0.25</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>38.7</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>52.85119174163302</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-358.65656689093</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>158.8907290696348</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1127,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1137,39 +1128,39 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:12</t>
+          <t>2026-06-16 11:20:17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:15</t>
+          <t>2026-06-16 11:20:17</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>3.13</v>
+        <v>0.03</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>72</v>
+        <v>27.3</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>367.140193872142</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>238.4883060488579</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>158.1612961552632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1191,39 +1182,39 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:15</t>
+          <t>2026-06-16 11:20:17</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:15</t>
+          <t>2026-06-16 11:20:17</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>12</v>
+        <v>31.6</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.31</v>
+        <v>0.46</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>76.5</v>
+        <v>17.3</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>415.1425336790175</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>91.44757487264189</v>
+        <v>0</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>159.1150437150943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1245,39 +1236,39 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:17</t>
+          <t>2026-06-16 17:58:13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:19</t>
+          <t>2026-06-16 17:58:17</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.33</v>
+        <v>3.34</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>12.1</v>
+        <v>26.9</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.74</v>
+        <v>0.49</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>73.7</v>
+        <v>16.1</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-103.6589047793671</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>-328.3314874315122</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>157.4625163612595</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1299,39 +1290,39 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:20</t>
+          <t>2026-06-16 17:58:19</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:20</t>
+          <t>2026-06-16 17:58:20</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>11.8</v>
+        <v>28.3</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>78.8</v>
+        <v>15.3</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-52.15671284567581</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-346.7492191563477</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>158.0247869494208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1353,39 +1344,39 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:20</t>
+          <t>2026-06-16 17:58:21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:20</t>
+          <t>2026-06-16 17:58:21</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
         <v>0.08</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>13.2</v>
+        <v>8.9</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>79.8</v>
+        <v>23.8</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-24.29955387147018</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-353.0668205535091</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>158.2862028460158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1407,39 +1398,39 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:21</t>
+          <t>2026-06-16 17:58:22</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:21</t>
+          <t>2026-06-16 17:58:22</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>12</v>
+        <v>30.2</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.53</v>
+        <v>0.28</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>171.3862910400345</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-334.126006273644</v>
+        <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>159.5526008850337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1461,39 +1452,39 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:22</t>
+          <t>2026-06-16 17:58:24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:22</t>
+          <t>2026-06-16 17:58:24</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>11.6</v>
+        <v>0.9</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>23.4</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>406.2406675615518</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-64.94020593570571</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>159.7359999180601</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1505,7 +1496,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1515,39 +1506,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:23</t>
+          <t>2026-06-16 17:58:29</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:23</t>
+          <t>2026-06-16 17:58:30</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.66</v>
+        <v>1.06</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>11.8</v>
+        <v>27.4</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>74.3</v>
+        <v>16.9</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>370.2841535153469</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>232.5809261024094</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>158.2086981205857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1569,39 +1560,39 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:23</t>
+          <t>2026-06-16 17:58:31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:24</t>
+          <t>2026-06-16 17:58:31</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.65</v>
+        <v>0.02</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>12.4</v>
+        <v>0.9</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.49</v>
+        <v>0.28</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>73</v>
+        <v>10.5</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>317.650514315408</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>311.1502494377624</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>157.4852516794919</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1623,39 +1614,39 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:24</t>
+          <t>2026-06-16 18:04:11</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:31</t>
+          <t>2026-06-16 18:04:12</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>6.95</v>
+        <v>1.38</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>12.4</v>
+        <v>19.7</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.86</v>
+        <v>0.5</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>71.2</v>
+        <v>19.1</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>29.72767461276764</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-358.7550607309078</v>
+        <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>158.7261036950252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1677,39 +1668,39 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:32</t>
+          <t>2026-06-16 18:04:13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:32</t>
+          <t>2026-06-16 18:04:13</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>12.8</v>
+        <v>23.3</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.26</v>
+        <v>0.41</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>73.2</v>
+        <v>15.9</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>-52.15166846454035</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-346.7505655854082</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>158.0248163273716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1731,39 +1722,39 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:32</t>
+          <t>2026-06-16 18:04:14</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:33</t>
+          <t>2026-06-16 18:04:15</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10.3</v>
+        <v>21.5</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>63.5</v>
+        <v>16.7</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>-118.056631387245</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>-321.4339714458717</v>
+        <v>0</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>157.2830277894036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1775,7 +1766,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1785,39 +1776,39 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:33</t>
+          <t>2026-06-16 18:04:16</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:33</t>
+          <t>2026-06-16 18:04:19</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.21</v>
+        <v>3.13</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>10.5</v>
+        <v>25.4</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>65.2</v>
+        <v>14.5</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>-111.421285924351</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-324.7161399390915</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>157.3670161978898</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1829,7 +1820,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1839,39 +1830,39 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:33</t>
+          <t>2026-06-16 18:04:20</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:33</t>
+          <t>2026-06-16 18:04:24</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.08</v>
+        <v>3.87</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>10.4</v>
+        <v>22.1</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>72.3</v>
+        <v>17.4</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>-103.6236673275074</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-328.3473744063875</v>
+        <v>0</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>157.4628458994333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1893,39 +1884,39 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:33</t>
+          <t>2026-06-16 18:04:25</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:34</t>
+          <t>2026-06-16 18:04:25</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10.4</v>
+        <v>20.4</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.28</v>
+        <v>0.53</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>62.7</v>
+        <v>15.5</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>-93.41583032696508</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-332.746349598383</v>
+        <v>0</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>157.5837175694251</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1937,7 +1928,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1947,39 +1938,39 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:34</t>
+          <t>2026-06-16 18:04:25</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:22:34</t>
+          <t>2026-06-16 18:04:27</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.09</v>
+        <v>1.81</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>10.4</v>
+        <v>21.6</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>63.3</v>
+        <v>20.8</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>-78.3093921079562</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-338.5535488268747</v>
+        <v>0</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>157.7534108541523</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1991,7 +1982,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2001,39 +1992,39 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:27:04</t>
+          <t>2026-06-16 18:04:27</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:27:07</t>
+          <t>2026-06-16 18:04:27</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>3.28</v>
+        <v>0.19</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>37.8</v>
+        <v>14.5</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.86</v>
+        <v>0.4</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>74.5</v>
+        <v>26.2</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>400.6011790672853</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>158.4479329304321</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>158.7336572215669</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2045,7 +2036,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2055,39 +2046,39 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:27:09</t>
+          <t>2026-06-16 18:04:27</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:27:12</t>
+          <t>2026-06-16 18:04:28</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>2.67</v>
+        <v>0.11</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>12.4</v>
+        <v>14.1</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.82</v>
+        <v>0.31</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>71.90000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>-117.7105141289481</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-321.6096498958875</v>
+        <v>0</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>157.2874379390676</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2099,7 +2090,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2114,25 +2105,25 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:31:12</t>
+          <t>2026-06-16 18:04:28</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:31:12</t>
+          <t>2026-06-16 18:04:30</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>14.2</v>
+        <v>18.7</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>68.40000000000001</v>
+        <v>23</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2153,7 +2144,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2168,25 +2159,25 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:31:12</t>
+          <t>2026-06-16 18:04:30</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:31:13</t>
+          <t>2026-06-16 18:04:32</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0.78</v>
+        <v>1.8</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>14.1</v>
+        <v>26.9</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.51</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>62.7</v>
+        <v>15.5</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2222,25 +2213,25 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:31:14</t>
+          <t>2026-06-16 18:04:32</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:31:14</t>
+          <t>2026-06-16 18:04:32</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>13.3</v>
+        <v>17.9</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>76.7</v>
+        <v>16.2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2276,25 +2267,25 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:31:14</t>
+          <t>2026-06-16 18:04:32</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:31:15</t>
+          <t>2026-06-16 18:04:32</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.73</v>
+        <v>0.29</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>14.1</v>
+        <v>30.2</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.52</v>
+        <v>0.39</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>63</v>
+        <v>14.7</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2315,7 +2306,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2330,25 +2321,25 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:40:46</t>
+          <t>2026-06-16 18:04:33</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:40:46</t>
+          <t>2026-06-16 18:04:41</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.08</v>
+        <v>7.94</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>15</v>
+        <v>26.8</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3</v>
+        <v>0.82</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>70.7</v>
+        <v>15.5</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2384,25 +2375,25 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:40:46</t>
+          <t>2026-06-16 18:04:42</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:40:46</t>
+          <t>2026-06-16 18:04:43</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.24</v>
+        <v>0.61</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>69.59999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2423,7 +2414,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2438,25 +2429,25 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:40:46</t>
+          <t>2026-06-16 18:04:43</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:40:49</t>
+          <t>2026-06-16 18:04:43</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>3.09</v>
+        <v>0.37</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13.7</v>
+        <v>26.8</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>64.8</v>
+        <v>13.6</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2492,25 +2483,25 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:40:50</t>
+          <t>2026-06-16 18:04:43</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:40:50</t>
+          <t>2026-06-16 18:04:43</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>12.7</v>
+        <v>5.8</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.33</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>63.7</v>
+        <v>14.3</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2531,7 +2522,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2546,25 +2537,25 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:40:51</t>
+          <t>2026-06-16 18:04:44</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:40:53</t>
+          <t>2026-06-16 18:04:44</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>2.09</v>
+        <v>0.08</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>13.8</v>
+        <v>40.4</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>62.8</v>
+        <v>11.6</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2600,25 +2591,25 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:46:08</t>
+          <t>2026-06-16 18:04:44</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:46:08</t>
+          <t>2026-06-16 18:04:44</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>11</v>
+        <v>15.4</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.27</v>
+        <v>0.64</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2654,25 +2645,25 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:46:08</t>
+          <t>2026-06-16 18:04:45</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:46:08</t>
+          <t>2026-06-16 18:04:45</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2708,25 +2699,25 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:46:08</t>
+          <t>2026-06-16 18:04:45</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:46:10</t>
+          <t>2026-06-16 18:04:48</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>1.8</v>
+        <v>3.11</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>12.8</v>
+        <v>30</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>69.8</v>
+        <v>14.1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2762,25 +2753,25 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:46:11</t>
+          <t>2026-06-16 18:04:50</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:46:11</t>
+          <t>2026-06-16 18:04:50</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="I43" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K43" s="2" t="n">
         <v>10.4</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>60.7</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2816,25 +2807,25 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:46:11</t>
+          <t>2026-06-16 18:04:50</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:46:14</t>
+          <t>2026-06-16 18:05:03</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>2.51</v>
+        <v>13.07</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>14.4</v>
+        <v>28.2</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>61.1</v>
+        <v>13.2</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2870,25 +2861,25 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:48:40</t>
+          <t>2026-06-16 18:05:03</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:48:40</t>
+          <t>2026-06-16 18:05:03</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10.5</v>
+        <v>31.7</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>15.1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2909,7 +2900,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2924,25 +2915,25 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:48:40</t>
+          <t>2026-06-16 18:05:04</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:48:44</t>
+          <t>2026-06-16 18:05:04</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>3.77</v>
+        <v>0.03</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>11.7</v>
+        <v>1.2</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.8</v>
+        <v>0.26</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>75.7</v>
+        <v>21.8</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2978,25 +2969,25 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:51:25</t>
+          <t>2026-06-16 18:05:05</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:51:25</t>
+          <t>2026-06-16 18:05:05</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -3032,25 +3023,25 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:51:25</t>
+          <t>2026-06-16 18:09:10</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:51:25</t>
+          <t>2026-06-16 18:09:10</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13.1</v>
+        <v>16.4</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>15.3</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3071,7 +3062,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3086,25 +3077,25 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:51:26</t>
+          <t>2026-06-16 18:09:10</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:51:28</t>
+          <t>2026-06-16 18:09:10</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>1.89</v>
+        <v>0.09</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>67.7</v>
+        <v>18.6</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3140,25 +3131,25 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:28</t>
+          <t>2026-06-16 18:09:11</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:32</t>
+          <t>2026-06-16 18:09:18</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>3.04</v>
+        <v>7.06</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>12.3</v>
+        <v>29</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>72.7</v>
+        <v>14.6</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3194,25 +3185,25 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:32</t>
+          <t>2026-06-16 18:09:18</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:32</t>
+          <t>2026-06-16 18:09:18</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>13.6</v>
+        <v>5.3</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>73</v>
+        <v>14.4</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3248,25 +3239,25 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:32</t>
+          <t>2026-06-16 18:09:18</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:32</t>
+          <t>2026-06-16 18:09:18</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0.16</v>
+        <v>0.44</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>12.9</v>
+        <v>33.3</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.34</v>
+        <v>0.41</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>70.5</v>
+        <v>11.8</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3287,7 +3278,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3302,25 +3293,25 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:32</t>
+          <t>2026-06-16 18:09:19</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:32</t>
+          <t>2026-06-16 18:09:29</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0.08</v>
+        <v>9.02</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>12.9</v>
+        <v>29.7</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.25</v>
+        <v>0.84</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>64.5</v>
+        <v>12.1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3356,25 +3347,25 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:33</t>
+          <t>2026-06-16 18:09:29</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:33</t>
+          <t>2026-06-16 18:09:29</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>13.9</v>
+        <v>31.9</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.26</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>63</v>
+        <v>10.2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3410,25 +3401,25 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:34</t>
+          <t>2026-06-16 18:09:29</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:34</t>
+          <t>2026-06-16 18:09:29</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12.9</v>
+        <v>31.3</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>66</v>
+        <v>10.2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3464,25 +3455,25 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:35</t>
+          <t>2026-06-16 18:09:29</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:35</t>
+          <t>2026-06-16 18:09:29</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>13.2</v>
+        <v>37.2</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>57.9</v>
+        <v>19.6</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3518,25 +3509,25 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:35</t>
+          <t>2026-06-16 18:09:30</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:35</t>
+          <t>2026-06-16 18:09:31</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>14.7</v>
+        <v>11.2</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>58.4</v>
+        <v>24.5</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3572,25 +3563,25 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:35</t>
+          <t>2026-06-16 18:09:31</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:35</t>
+          <t>2026-06-16 18:09:31</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>14.6</v>
+        <v>31</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.52</v>
+        <v>0.39</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>21.1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3626,25 +3617,25 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:36</t>
+          <t>2026-06-16 18:09:31</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:36</t>
+          <t>2026-06-16 18:09:31</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13.2</v>
+        <v>29.5</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.37</v>
+        <v>0.28</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>57.9</v>
+        <v>21.3</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3680,25 +3671,25 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:36</t>
+          <t>2026-06-16 18:09:31</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:36</t>
+          <t>2026-06-16 18:09:31</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.22</v>
+        <v>0.03</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>14.6</v>
+        <v>37.9</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.58</v>
+        <v>0.45</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>66.09999999999999</v>
+        <v>18.9</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3734,25 +3725,25 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:36</t>
+          <t>2026-06-16 18:09:32</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:36</t>
+          <t>2026-06-16 18:09:32</t>
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>15.3</v>
+        <v>17.1</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>60.1</v>
+        <v>19.2</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3788,25 +3779,25 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:38</t>
+          <t>2026-06-16 18:09:32</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:38</t>
+          <t>2026-06-16 18:09:32</t>
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>14.4</v>
+        <v>32.8</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>57.8</v>
+        <v>19.1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3842,25 +3833,25 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:39</t>
+          <t>2026-06-16 18:09:32</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:39</t>
+          <t>2026-06-16 18:09:32</t>
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15.7</v>
+        <v>35.5</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>64.5</v>
+        <v>18.9</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3896,25 +3887,25 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:40</t>
+          <t>2026-06-16 18:09:33</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:40</t>
+          <t>2026-06-16 18:09:33</t>
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0.44</v>
+        <v>0.03</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>13.7</v>
+        <v>38.1</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>63.3</v>
+        <v>19.2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3950,25 +3941,25 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:41</t>
+          <t>2026-06-16 18:09:33</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:41</t>
+          <t>2026-06-16 18:09:33</t>
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>69.8</v>
+        <v>19</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -4004,25 +3995,25 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:41</t>
+          <t>2026-06-16 18:09:33</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:41</t>
+          <t>2026-06-16 18:09:33</t>
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>0.14</v>
+        <v>0.03</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>15.6</v>
+        <v>31.8</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.47</v>
+        <v>0.3</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>56.5</v>
+        <v>18.5</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -4058,25 +4049,25 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:41</t>
+          <t>2026-06-16 18:09:34</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:41</t>
+          <t>2026-06-16 18:09:34</t>
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>8.9</v>
+        <v>31.3</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>56</v>
+        <v>18.9</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4097,7 +4088,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4112,25 +4103,25 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:41</t>
+          <t>2026-06-16 18:09:34</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 20:55:45</t>
+          <t>2026-06-16 18:09:34</t>
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>3.32</v>
+        <v>0.06</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>13.9</v>
+        <v>17.5</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>62</v>
+        <v>18.7</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4151,7 +4142,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4161,39 +4152,39 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:05:14</t>
+          <t>2026-06-16 18:09:35</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:05:17</t>
+          <t>2026-06-16 18:09:35</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>2.75</v>
+        <v>0.03</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>10.9</v>
+        <v>31.6</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.65</v>
+        <v>0.54</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>81.09999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>400.4235817509426</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>159.0316816861704</v>
+        <v>0</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>158.7298736619315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4215,39 +4206,39 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:05:18</t>
+          <t>2026-06-16 18:09:36</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:05:18</t>
+          <t>2026-06-16 18:09:36</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>11.2</v>
+        <v>31.7</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>84.09999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>342.7563957311527</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>278.215735454211</v>
+        <v>0</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>157.8148512595829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4269,39 +4260,39 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:05:19</t>
+          <t>2026-06-16 18:09:36</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:05:19</t>
+          <t>2026-06-16 18:09:36</t>
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10.9</v>
+        <v>30.8</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>85.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>374.3274745193712</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>224.6417217171535</v>
+        <v>0</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>158.2711735738418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4313,7 +4304,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4323,39 +4314,39 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:05:19</t>
+          <t>2026-06-16 18:09:36</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:05:21</t>
+          <t>2026-06-16 18:09:36</t>
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>1.64</v>
+        <v>0.04</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>10.9</v>
+        <v>39.2</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7</v>
+        <v>0.27</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>82</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>398.7476594641733</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-90.85078889359116</v>
+        <v>0</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>159.804257784948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4367,7 +4358,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4377,39 +4368,39 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>cobot</t>
+          <t>no cobot</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:05:21</t>
+          <t>2026-06-16 18:09:37</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:05:30</t>
+          <t>2026-06-16 18:09:37</t>
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>9.210000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>12.1</v>
+        <v>31</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.87</v>
+        <v>0.27</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>12.6</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>-115.0089114048076</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-322.9639538460081</v>
+        <v>0</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>157.3219386993865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4421,7 +4412,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4436,25 +4427,25 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:08:45</t>
+          <t>2026-06-16 18:09:37</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:08:49</t>
+          <t>2026-06-16 18:09:37</t>
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>3.43</v>
+        <v>0.03</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>10.7</v>
+        <v>31.7</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.84</v>
+        <v>0.31</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>105.1</v>
+        <v>11.2</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4490,25 +4481,25 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:08:49</t>
+          <t>2026-06-16 18:09:38</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:08:49</t>
+          <t>2026-06-16 18:09:38</t>
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>0.49</v>
+        <v>0.02</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>12.3</v>
+        <v>30.6</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.57</v>
+        <v>0.27</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>73.5</v>
+        <v>11.9</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4544,25 +4535,25 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:08:50</t>
+          <t>2026-06-16 18:09:38</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:08:51</t>
+          <t>2026-06-16 18:09:38</t>
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>0.23</v>
+        <v>0.02</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>13.1</v>
+        <v>5.9</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>11.7</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4583,7 +4574,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4598,25 +4589,25 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:08:51</t>
+          <t>2026-06-16 18:09:39</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:08:56</t>
+          <t>2026-06-16 18:09:39</t>
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>4.85</v>
+        <v>0.02</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>13.9</v>
+        <v>31.5</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>63.6</v>
+        <v>13</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4637,7 +4628,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4652,25 +4643,25 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:08:59</t>
+          <t>2026-06-16 18:09:39</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:03</t>
+          <t>2026-06-16 18:09:39</t>
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>4.06</v>
+        <v>0.03</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>13.9</v>
+        <v>31.4</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.82</v>
+        <v>0.28</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>63.6</v>
+        <v>12.6</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4706,25 +4697,25 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:03</t>
+          <t>2026-06-16 18:09:39</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:03</t>
+          <t>2026-06-16 18:09:39</t>
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>0.36</v>
+        <v>0.06</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>13.3</v>
+        <v>32.9</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>12.7</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4745,7 +4736,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4760,25 +4751,25 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:05</t>
+          <t>2026-06-16 18:09:40</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:11</t>
+          <t>2026-06-16 18:09:40</t>
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>5.64</v>
+        <v>0.03</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.4</v>
+        <v>32.1</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.87</v>
+        <v>0.34</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>61</v>
+        <v>23.4</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4814,25 +4805,25 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:12</t>
+          <t>2026-06-16 18:09:41</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:13</t>
+          <t>2026-06-16 18:09:41</t>
         </is>
       </c>
       <c r="H81" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>14.4</v>
+        <v>31.5</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.68</v>
+        <v>0.34</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>61.7</v>
+        <v>9</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4868,25 +4859,25 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:13</t>
+          <t>2026-06-16 18:09:41</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:14</t>
+          <t>2026-06-16 18:09:41</t>
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>0.75</v>
+        <v>0.02</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.6</v>
+        <v>30.9</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>66.09999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4922,25 +4913,25 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:14</t>
+          <t>2026-06-16 18:09:42</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:14</t>
+          <t>2026-06-16 18:09:42</t>
         </is>
       </c>
       <c r="H83" s="2" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.7</v>
+        <v>31.9</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>59.1</v>
+        <v>8.5</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4976,25 +4967,25 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:16</t>
+          <t>2026-06-16 18:09:42</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:16</t>
+          <t>2026-06-16 18:09:42</t>
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>0.37</v>
+        <v>0.02</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>12.8</v>
+        <v>31.8</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>67.2</v>
+        <v>10</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -5030,25 +5021,25 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:17</t>
+          <t>2026-06-16 18:09:43</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:18</t>
+          <t>2026-06-16 18:09:43</t>
         </is>
       </c>
       <c r="H85" s="2" t="n">
-        <v>0.49</v>
+        <v>0.02</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>10.3</v>
+        <v>20.8</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>88.7</v>
+        <v>10</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -5084,25 +5075,25 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:18</t>
+          <t>2026-06-16 18:09:43</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:18</t>
+          <t>2026-06-16 18:09:43</t>
         </is>
       </c>
       <c r="H86" s="2" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>10.4</v>
+        <v>42.5</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.43</v>
+        <v>0.35</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>81.3</v>
+        <v>10.3</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5138,25 +5129,25 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:19</t>
+          <t>2026-06-16 18:09:43</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:19</t>
+          <t>2026-06-16 18:09:43</t>
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>12.2</v>
+        <v>55.1</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.29</v>
+        <v>0.51</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5192,25 +5183,25 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:19</t>
+          <t>2026-06-16 18:09:44</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:20</t>
+          <t>2026-06-16 18:09:44</t>
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>0.68</v>
+        <v>0.02</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.1</v>
+        <v>31.3</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.73</v>
+        <v>0.35</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5246,25 +5237,25 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:21</t>
+          <t>2026-06-16 18:09:44</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:21</t>
+          <t>2026-06-16 18:09:44</t>
         </is>
       </c>
       <c r="H89" s="2" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.4</v>
+        <v>5.9</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.49</v>
+        <v>0.33</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>83.8</v>
+        <v>12.4</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5300,25 +5291,25 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:21</t>
+          <t>2026-06-16 18:09:44</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:21</t>
+          <t>2026-06-16 18:09:44</t>
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>0.26</v>
+        <v>0.02</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>11.7</v>
+        <v>6.1</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>77.5</v>
+        <v>12.9</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5354,25 +5345,25 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:21</t>
+          <t>2026-06-16 18:09:44</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:21</t>
+          <t>2026-06-16 18:09:44</t>
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.5</v>
+        <v>30.8</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.29</v>
+        <v>0.48</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>84</v>
+        <v>22.4</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5408,25 +5399,25 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:22</t>
+          <t>2026-06-16 18:09:45</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:23</t>
+          <t>2026-06-16 18:09:45</t>
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>0.72</v>
+        <v>0.03</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11.6</v>
+        <v>5.1</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.62</v>
+        <v>0.36</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>78.5</v>
+        <v>19.3</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5462,25 +5453,25 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:23</t>
+          <t>2026-06-16 18:09:45</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:09:23</t>
+          <t>2026-06-16 18:09:45</t>
         </is>
       </c>
       <c r="H93" s="2" t="n">
-        <v>0.43</v>
+        <v>0.1</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>11.1</v>
+        <v>26.5</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.66</v>
+        <v>0.39</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>80.3</v>
+        <v>19.2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5501,7 +5492,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5516,25 +5507,25 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:11:53</t>
+          <t>2026-06-16 18:09:45</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:11:58</t>
+          <t>2026-06-16 18:09:45</t>
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>4.25</v>
+        <v>0.06</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>18.8</v>
+        <v>34.9</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.79</v>
+        <v>0.32</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>86.59999999999999</v>
+        <v>13.3</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5570,25 +5561,25 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:00</t>
+          <t>2026-06-16 18:09:46</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:00</t>
+          <t>2026-06-16 18:09:46</t>
         </is>
       </c>
       <c r="H95" s="2" t="n">
-        <v>0.29</v>
+        <v>0.03</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>13.7</v>
+        <v>32.8</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>63.9</v>
+        <v>7.9</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5624,25 +5615,25 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:01</t>
+          <t>2026-06-16 18:09:48</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:01</t>
+          <t>2026-06-16 18:09:48</t>
         </is>
       </c>
       <c r="H96" s="2" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13.5</v>
+        <v>31.1</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>64.5</v>
+        <v>12.6</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5663,7 +5654,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5678,25 +5669,25 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:04</t>
+          <t>2026-06-16 18:09:49</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:06</t>
+          <t>2026-06-16 18:09:49</t>
         </is>
       </c>
       <c r="H97" s="2" t="n">
-        <v>2.11</v>
+        <v>0.02</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>13.5</v>
+        <v>20.9</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>66.59999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5732,25 +5723,25 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:06</t>
+          <t>2026-06-16 18:09:50</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:06</t>
+          <t>2026-06-16 18:09:50</t>
         </is>
       </c>
       <c r="H98" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>12.7</v>
+        <v>30.9</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.29</v>
+        <v>0.58</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5771,7 +5762,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -5786,25 +5777,25 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:08</t>
+          <t>2026-06-16 18:09:51</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:10</t>
+          <t>2026-06-16 18:09:51</t>
         </is>
       </c>
       <c r="H99" s="2" t="n">
-        <v>1.97</v>
+        <v>0.02</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.3</v>
+        <v>31.2</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>66.8</v>
+        <v>14.9</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5825,7 +5816,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -5840,25 +5831,25 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:11</t>
+          <t>2026-06-19 13:06:22</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:11</t>
+          <t>2026-06-19 13:06:29</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>0.08</v>
+        <v>6.69</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>14.9</v>
+        <v>35.3</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.32</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>63</v>
+        <v>13.4</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5879,7 +5870,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -5894,25 +5885,25 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:12</t>
+          <t>2026-06-19 13:06:29</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:13</t>
+          <t>2026-06-19 13:06:29</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
-        <v>1.69</v>
+        <v>0.09</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>13</v>
+        <v>30.9</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.62</v>
+        <v>0.26</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5933,7 +5924,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -5948,25 +5939,25 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:15</t>
+          <t>2026-06-19 13:06:29</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:12:17</t>
+          <t>2026-06-19 13:06:29</t>
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>1.92</v>
+        <v>0.05</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.8</v>
+        <v>30.6</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.65</v>
+        <v>0.27</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>64.59999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5983,11 +5974,11 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -6002,25 +5993,25 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:06:29</t>
+          <t>2026-06-19 13:06:29</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:06:42</t>
+          <t>2026-06-19 13:06:30</t>
         </is>
       </c>
       <c r="H103" s="2" t="n">
-        <v>12.94</v>
+        <v>0.2</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>10.2</v>
+        <v>31.3</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.86</v>
+        <v>0.26</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>94.2</v>
+        <v>13.7</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -6037,7 +6028,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
@@ -6056,25 +6047,25 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:06:44</t>
+          <t>2026-06-19 13:06:30</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:06:44</t>
+          <t>2026-06-19 13:06:30</t>
         </is>
       </c>
       <c r="H104" s="2" t="n">
         <v>0.09</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.2</v>
+        <v>31.6</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>83.8</v>
+        <v>13.2</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -6091,7 +6082,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
@@ -6110,25 +6101,25 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:06:44</t>
+          <t>2026-06-19 13:06:30</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:06:44</t>
+          <t>2026-06-19 13:06:30</t>
         </is>
       </c>
       <c r="H105" s="2" t="n">
         <v>0.08</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>11.2</v>
+        <v>31.2</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.27</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>75.5</v>
+        <v>12.3</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6145,11 +6136,11 @@
         <v>105</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -6164,25 +6155,25 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:06:46</t>
+          <t>2026-06-19 13:06:30</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:07:13</t>
+          <t>2026-06-19 13:06:30</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
-        <v>27.56</v>
+        <v>0.13</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>10.9</v>
+        <v>28.6</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.91</v>
+        <v>0.26</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>82.3</v>
+        <v>12</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6199,11 +6190,11 @@
         <v>106</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -6218,25 +6209,25 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:07:17</t>
+          <t>2026-06-19 13:06:30</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:07:27</t>
+          <t>2026-06-19 13:06:30</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>9.77</v>
+        <v>0.06</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>11.4</v>
+        <v>31.5</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.88</v>
+        <v>0.26</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>78</v>
+        <v>10.9</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6253,11 +6244,11 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -6272,25 +6263,25 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:07:32</t>
+          <t>2026-06-19 13:06:30</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:07:45</t>
+          <t>2026-06-19 13:06:30</t>
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>13.51</v>
+        <v>0.09</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>11.3</v>
+        <v>31.6</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.92</v>
+        <v>0.26</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>78.2</v>
+        <v>10.5</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6307,11 +6298,11 @@
         <v>108</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -6326,25 +6317,25 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:07:48</t>
+          <t>2026-06-19 13:06:30</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:07:53</t>
+          <t>2026-06-19 13:06:30</t>
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>5.17</v>
+        <v>0.04</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>11.7</v>
+        <v>31.6</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>76.2</v>
+        <v>10.3</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6361,11 +6352,11 @@
         <v>109</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>detection</t>
+          <t>requires checking</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -6380,25 +6371,25 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:07:55</t>
+          <t>2026-06-19 13:06:31</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 17:08:04</t>
+          <t>2026-06-19 13:06:31</t>
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>9.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>11.8</v>
+        <v>35.3</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>75</v>
+        <v>12.4</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6415,7 +6406,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
@@ -6434,25 +6425,25 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:17:23</t>
+          <t>2026-06-19 13:06:31</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:17:32</t>
+          <t>2026-06-19 13:06:32</t>
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>24.7</v>
+        <v>30.4</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.88</v>
+        <v>0.52</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>16.9</v>
+        <v>13</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6469,7 +6460,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
@@ -6488,25 +6479,25 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:17:33</t>
+          <t>2026-06-19 13:06:34</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:17:35</t>
+          <t>2026-06-19 13:06:39</t>
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>2.08</v>
+        <v>4.12</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>24</v>
+        <v>30.7</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6523,7 +6514,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
@@ -6542,25 +6533,25 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:17:37</t>
+          <t>2026-06-19 13:06:41</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>2026-06-14 22:17:39</t>
+          <t>2026-06-19 13:06:44</t>
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>2.09</v>
+        <v>3.73</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>24</v>
+        <v>30.5</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6581,7 +6572,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -6596,25 +6587,25 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 10:41:49</t>
+          <t>2026-06-19 13:06:47</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 10:41:49</t>
+          <t>2026-06-19 13:06:50</t>
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>0.04</v>
+        <v>3.38</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>20.5</v>
+        <v>30.1</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.31</v>
+        <v>0.85</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6635,7 +6626,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -6650,25 +6641,25 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 10:41:49</t>
+          <t>2026-06-19 13:06:52</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 10:41:49</t>
+          <t>2026-06-19 13:06:55</t>
         </is>
       </c>
       <c r="H115" s="2" t="n">
-        <v>0.06</v>
+        <v>2.92</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>12.5</v>
+        <v>30.7</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.38</v>
+        <v>0.87</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>10.8</v>
+        <v>12</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6689,7 +6680,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -6704,25 +6695,25 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 10:41:52</t>
+          <t>2026-06-19 13:06:58</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 10:41:52</t>
+          <t>2026-06-19 13:07:01</t>
         </is>
       </c>
       <c r="H116" s="2" t="n">
-        <v>0.2</v>
+        <v>3.19</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>15.6</v>
+        <v>30.6</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.41</v>
+        <v>0.85</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>9.1</v>
+        <v>11.8</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6743,7 +6734,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -6758,25 +6749,25 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 10:41:52</t>
+          <t>2026-06-19 13:07:03</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 10:41:52</t>
+          <t>2026-06-19 13:07:06</t>
         </is>
       </c>
       <c r="H117" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.22</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>10.4</v>
+        <v>30.5</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.47</v>
+        <v>0.85</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>16.4</v>
+        <v>11.6</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6797,7 +6788,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>requires checking</t>
+          <t>detection</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -6812,25 +6803,25 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 10:41:53</t>
+          <t>2026-06-19 13:07:08</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 10:41:53</t>
+          <t>2026-06-19 13:07:11</t>
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>0.03</v>
+        <v>2.99</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>30.8</v>
+        <v>30.5</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.27</v>
+        <v>0.85</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>20.9</v>
+        <v>12.5</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6839,1572 +6830,6 @@
         <v>0</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:04</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:06</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K119" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="L119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N119" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:09</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:11</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="K120" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N120" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:14</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:17</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="K121" s="2" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:18</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:21</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:22</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:25</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="K123" s="2" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N123" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
-        <v>123</v>
-      </c>
-      <c r="B124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:27</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:30</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="K124" s="2" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N124" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:31</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:37</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="J125" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="K125" s="2" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N125" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>requires checking</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:39</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:42:39</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J126" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="K126" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N126" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:08</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:11</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="I127" s="2" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="J127" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="K127" s="2" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N127" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:13</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:16</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="I128" s="2" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="J128" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="K128" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="L128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N128" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:18</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:20</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="I129" s="2" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="J129" s="2" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="K129" s="2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="L129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N129" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:22</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:25</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="I130" s="2" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="J130" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="K130" s="2" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="L130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N130" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="B131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:27</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:29</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="J131" s="2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="K131" s="2" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="L131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N131" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:31</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:36</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="J132" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K132" s="2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="L132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N132" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>requires checking</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:38</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:38</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="J133" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="K133" s="2" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="L133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N133" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>requires checking</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:38</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:38</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I134" s="2" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J134" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="K134" s="2" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="L134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>requires checking</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:39</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:39</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J135" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="K135" s="2" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="L135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>requires checking</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:58</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:58</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I136" s="2" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="J136" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="K136" s="2" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="L136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>detection</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:54:58</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:55:02</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="I137" s="2" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="J137" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="K137" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>requires checking</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:55:04</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:55:04</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="J138" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="K138" s="2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>requires checking</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:18</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:18</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I139" s="2" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="J139" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="K139" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="L139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>requires checking</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:18</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:18</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I140" s="2" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="J140" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="K140" s="2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N140" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>requires checking</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:19</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:19</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I141" s="2" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="J141" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K141" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="L141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
-        <v>141</v>
-      </c>
-      <c r="B142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>requires checking</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:20</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:20</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I142" s="2" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="J142" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K142" s="2" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="L142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>requires checking</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:22</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:22</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I143" s="2" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="J143" s="2" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="K143" s="2" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="L143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="B144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>requires checking</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:23</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:23</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I144" s="2" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="J144" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="K144" s="2" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="L144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N144" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="B145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>requires checking</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:24</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:25</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I145" s="2" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="K145" s="2" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N145" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="B146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>requires checking</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:26</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:27</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I146" s="2" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="J146" s="2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="K146" s="2" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="L146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N146" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>requires checking</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>yolov8n-pose.pt</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>no cobot</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:28</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16 10:58:28</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="I147" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="K147" s="2" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="L147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N147" s="2" t="n">
         <v>0</v>
       </c>
     </row>
